--- a/artfynd/A 13908-2026 artfynd.xlsx
+++ b/artfynd/A 13908-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385527</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385535</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385522</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385528</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385530</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385515</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1798,6 +1848,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385516</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385526</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385532</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2155,6 +2220,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385533</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2266,6 +2336,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385524</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2377,8 +2452,30 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 13908-2026 artfynd.xlsx
+++ b/artfynd/A 13908-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135385527</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135385518</v>
       </c>
       <c r="B3" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135385535</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135385517</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135385520</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135385522</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135385528</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135385530</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135385515</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>135385516</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>135385526</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135385532</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135385533</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135385524</v>
       </c>
       <c r="B15" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>135385534</v>
       </c>
       <c r="B16" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 13908-2026 artfynd.xlsx
+++ b/artfynd/A 13908-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135385527</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135385518</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135385535</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135385517</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135385520</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135385522</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135385528</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135385530</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135385524</v>
       </c>
       <c r="B15" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>135385534</v>
       </c>
       <c r="B16" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 13908-2026 artfynd.xlsx
+++ b/artfynd/A 13908-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135385527</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135385518</v>
       </c>
       <c r="B3" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135385535</v>
       </c>
       <c r="B4" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135385524</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>135385534</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
